--- a/virtual_event_forms/033_virtual_webinar_registration_form--virtual_event_forms.xlsx
+++ b/virtual_event_forms/033_virtual_webinar_registration_form--virtual_event_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1052,12 +1052,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'est',_'label':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'EST', 'label': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'cst',_'label':_'cst'}</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'CST', 'label': 'CST'}</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'pst',_'label':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'PST', 'label': 'PST'}</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'mdt',_'label':_'mdt'}</t>
+          <t>mdt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'MDT', 'label': 'MDT'}</t>
+          <t>MDT</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'edt',_'label':_'edt'}</t>
+          <t>edt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'EDT', 'label': 'EDT'}</t>
+          <t>EDT</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'cdt',_'label':_'cdt'}</t>
+          <t>cdt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'CDT', 'label': 'CDT'}</t>
+          <t>CDT</t>
         </is>
       </c>
     </row>
@@ -1187,29 +1187,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'value':_'cst',_'label':_'cst'}</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'value': 'CST', 'label': 'CST'}</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time_zone_choices</t>
+          <t>select_question_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'value':_'mst',_'label':_'mst'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'value': 'MST', 'label': 'MST'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_1,_'label':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 1, 'label': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1238,29 +1238,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_2,_'label':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 2, 'label': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_question_choices</t>
+          <t>select_question_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'option_3'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Option 3'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1272,29 +1272,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_question_2_choices</t>
+          <t>select_question_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1306,29 +1306,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_question_3_choices</t>
+          <t>select_question_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1340,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_question_4_choices</t>
+          <t>select_question_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1374,29 +1374,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_question_5_choices</t>
+          <t>select_question_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1408,29 +1408,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_question_6_choices</t>
+          <t>select_question_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1442,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_question_7_choices</t>
+          <t>select_question_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1476,29 +1476,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_question_8_choices</t>
+          <t>select_question_9_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1510,29 +1510,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_question_9_choices</t>
+          <t>select_question_10_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1544,29 +1544,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_question_10_choices</t>
+          <t>select_question_11_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1578,29 +1578,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_question_11_choices</t>
+          <t>select_question_12_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1612,29 +1612,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_question_12_choices</t>
+          <t>select_question_13_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1646,29 +1646,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_question_13_choices</t>
+          <t>select_question_14_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1680,27 +1680,10 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_question_14_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
         <is>
           <t>No</t>
         </is>
